--- a/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T14:37:21+00:00</t>
+    <t>2025-01-06T16:21:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:21:28+00:00</t>
+    <t>2025-01-07T10:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T10:53:29+00:00</t>
+    <t>2025-01-07T12:05:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T12:05:20+00:00</t>
+    <t>2025-01-10T09:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-10T09:39:42+00:00</t>
+    <t>2025-01-20T10:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-JANVIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T10:44:30+00:00</t>
+    <t>2025-01-31T15:38:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
